--- a/book_mapping.xlsx
+++ b/book_mapping.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="614">
   <si>
     <t>ローマ字ファイル名</t>
   </si>
@@ -19,9 +19,15 @@
     <t>日本語書籍名</t>
   </si>
   <si>
+    <t>日本語書籍名読み</t>
+  </si>
+  <si>
     <t>著者名</t>
   </si>
   <si>
+    <t>著者名読み</t>
+  </si>
+  <si>
     <t>知名度スコア</t>
   </si>
   <si>
@@ -40,9 +46,15 @@
     <t>檸檬</t>
   </si>
   <si>
+    <t>れもん</t>
+  </si>
+  <si>
     <t>梶井基次郎</t>
   </si>
   <si>
+    <t>かじいもとじろう</t>
+  </si>
+  <si>
     <t>純文学</t>
   </si>
   <si>
@@ -55,9 +67,15 @@
     <t>銀河鉄道の夜</t>
   </si>
   <si>
+    <t>ぎんがてつどうのよる</t>
+  </si>
+  <si>
     <t>宮沢賢治</t>
   </si>
   <si>
+    <t>みやざわけんじ</t>
+  </si>
+  <si>
     <t>童話</t>
   </si>
   <si>
@@ -70,9 +88,15 @@
     <t>吾輩は猫である</t>
   </si>
   <si>
+    <t>わがはいはねこである</t>
+  </si>
+  <si>
     <t>夏目漱石</t>
   </si>
   <si>
+    <t>なつめそうせき</t>
+  </si>
+  <si>
     <t>猫の視点から主人の苦沙弥先生やその友人たちの人間模様を風刺的かつコミカルに描いた作品。</t>
   </si>
   <si>
@@ -82,9 +106,15 @@
     <t>走れメロス</t>
   </si>
   <si>
+    <t>はしれめろす</t>
+  </si>
+  <si>
     <t>太宰治</t>
   </si>
   <si>
+    <t>だざいおさむ</t>
+  </si>
+  <si>
     <t>処刑される友を救うため邪智暴虐の王との約束を果たそうとメロスが走り続ける友情の物語。</t>
   </si>
   <si>
@@ -94,9 +124,15 @@
     <t>羅生門</t>
   </si>
   <si>
+    <t>らしょうもん</t>
+  </si>
+  <si>
     <t>芥川龍之介</t>
   </si>
   <si>
+    <t>あくたがわりゅうのすけ</t>
+  </si>
+  <si>
     <t>荒廃した羅生門の下で生きるための悪と倫理の狭間で葛藤する下人の心理を描いた短編。</t>
   </si>
   <si>
@@ -106,9 +142,15 @@
     <t>舞姫</t>
   </si>
   <si>
+    <t>まいひめ</t>
+  </si>
+  <si>
     <t>森鴎外</t>
   </si>
   <si>
+    <t>もりおうがい</t>
+  </si>
+  <si>
     <t>ドイツ留学中のエリート官僚である豊太郎が美しい踊子エリスとの恋と立身出世の間で苦悩する。</t>
   </si>
   <si>
@@ -118,9 +160,15 @@
     <t>人間椅子</t>
   </si>
   <si>
+    <t>にんげんいす</t>
+  </si>
+  <si>
     <t>江戸川乱歩</t>
   </si>
   <si>
+    <t>えどがわらんぽ</t>
+  </si>
+  <si>
     <t>推理・SF</t>
   </si>
   <si>
@@ -133,9 +181,15 @@
     <t>高野聖</t>
   </si>
   <si>
+    <t>こうやひじり</t>
+  </si>
+  <si>
     <t>泉鏡花</t>
   </si>
   <si>
+    <t>いずみきょうか</t>
+  </si>
+  <si>
     <t>飛騨の山奥で迷った僧が妖艶な美女の住む孤家で不可思議な体験をする幻想的かつ浪漫的な物語。</t>
   </si>
   <si>
@@ -145,9 +199,15 @@
     <t>桜の森の満開の下</t>
   </si>
   <si>
+    <t>さくらのもりのまんかいのした</t>
+  </si>
+  <si>
     <t>坂口安吾</t>
   </si>
   <si>
+    <t>さかぐちあんご</t>
+  </si>
+  <si>
     <t>桜の森の満開の下で恐ろしい孤独と狂気に囚われていく山賊と残酷な美女の凄惨な愛の結末。</t>
   </si>
   <si>
@@ -157,9 +217,15 @@
     <t>山月記</t>
   </si>
   <si>
+    <t>さんげつき</t>
+  </si>
+  <si>
     <t>中島敦</t>
   </si>
   <si>
+    <t>なかじまあつし</t>
+  </si>
+  <si>
     <t>自尊心と臆病さから虎に変身してしまった詩人李徴がかつての友に己の数奇な運命を語る。</t>
   </si>
   <si>
@@ -169,9 +235,15 @@
     <t>夜明け前（第二部下）</t>
   </si>
   <si>
+    <t>よあけまえだいにぶげ</t>
+  </si>
+  <si>
     <t>島崎藤村</t>
   </si>
   <si>
+    <t>しまざきとうそん</t>
+  </si>
+  <si>
     <t>激動の幕末から明治維新を生き抜いた青山半蔵の理想と挫折を描く歴史大河小説の最終部。</t>
   </si>
   <si>
@@ -181,6 +253,9 @@
     <t>堺事件</t>
   </si>
   <si>
+    <t>さかいじけん</t>
+  </si>
+  <si>
     <t>幕末の堺で起こったフランス水兵殺傷事件と命じられた土佐藩士たちの切腹を史実に基づき描く。</t>
   </si>
   <si>
@@ -190,9 +265,15 @@
     <t>卍</t>
   </si>
   <si>
+    <t>まんじ</t>
+  </si>
+  <si>
     <t>谷崎潤一郎</t>
   </si>
   <si>
+    <t>たにざきじゅんいちろう</t>
+  </si>
+  <si>
     <t>美貌の女性を中心に四人の男女が複雑に絡み合う愛憎と破滅への道程を描いた官能的な物語。</t>
   </si>
   <si>
@@ -202,6 +283,9 @@
     <t>よだかの星</t>
   </si>
   <si>
+    <t>よだかのほし</t>
+  </si>
+  <si>
     <t>醜い姿ゆえに鳥たちから迫害されたよだかが自らの命を燃やし夜空の美しい星となるまで。</t>
   </si>
   <si>
@@ -211,6 +295,9 @@
     <t>陰獣</t>
   </si>
   <si>
+    <t>いんじゅう</t>
+  </si>
+  <si>
     <t>探偵小説家である私が同じく作家の大江春泥と名乗る男の犯罪計画に巻き込まれていく心理的恐怖。</t>
   </si>
   <si>
@@ -220,6 +307,9 @@
     <t>黄金仮面</t>
   </si>
   <si>
+    <t>おうごんかめん</t>
+  </si>
+  <si>
     <t>黄金の仮面を被った謎の怪盗と名探偵明智小五郎が知恵比べを繰り広げるスリリングな活劇。</t>
   </si>
   <si>
@@ -229,6 +319,9 @@
     <t>細雪（下巻）</t>
   </si>
   <si>
+    <t>ささめゆきげかん</t>
+  </si>
+  <si>
     <t>大阪の旧家蒔岡家の四姉妹の日常と三女雪子の見合い話の顛末を描く絢爛たる絵巻物の完結編。</t>
   </si>
   <si>
@@ -238,6 +331,9 @@
     <t>猫と庄造と二人のをんな</t>
   </si>
   <si>
+    <t>ねことしょうぞうとふたりのをんな</t>
+  </si>
+  <si>
     <t>一匹の猫を巡って優柔不断な男と元妻そして新妻の三者が繰り広げる滑稽で皮肉な心理戦。</t>
   </si>
   <si>
@@ -247,6 +343,9 @@
     <t>富嶽百景</t>
   </si>
   <si>
+    <t>ふがくひゃっけい</t>
+  </si>
+  <si>
     <t>富士山を背景に人生に思い悩む作者自身の姿や周囲の人々との交流を私小説風に綴った傑作。</t>
   </si>
   <si>
@@ -256,6 +355,9 @@
     <t>春琴抄</t>
   </si>
   <si>
+    <t>しゅんきんしょう</t>
+  </si>
+  <si>
     <t>盲目で我儘な三味線の師匠春琴と彼女に絶対的な献身を捧げる奉公人佐助の歪で美しい愛の形。</t>
   </si>
   <si>
@@ -265,6 +367,9 @@
     <t>細雪（中巻）</t>
   </si>
   <si>
+    <t>ささめゆきちゅうかん</t>
+  </si>
+  <si>
     <t>没落しつつある関西の良家蒔岡家の四姉妹の美しくも哀愁漂う人間模様を精緻に描いた中巻。</t>
   </si>
   <si>
@@ -274,6 +379,9 @@
     <t>蓼喰う虫</t>
   </si>
   <si>
+    <t>たでくうむし</t>
+  </si>
+  <si>
     <t>愛情の冷え切った夫婦が離婚に至るまでの微細な心理の揺れ動きと倦怠の情景を描く。</t>
   </si>
   <si>
@@ -283,9 +391,15 @@
     <t>やみ夜</t>
   </si>
   <si>
+    <t>やみよ</t>
+  </si>
+  <si>
     <t>樋口一葉</t>
   </si>
   <si>
+    <t>ひぐちいちよう</t>
+  </si>
+  <si>
     <t>社会の底辺で生きる人々の悲哀と絶望を暗い夜の闇に重ね合わせて描いた初期の短編小説。</t>
   </si>
   <si>
@@ -295,9 +409,15 @@
     <t>死後の恋</t>
   </si>
   <si>
+    <t>しごのこい</t>
+  </si>
+  <si>
     <t>夢野久作</t>
   </si>
   <si>
+    <t>ゆめのきゅうさく</t>
+  </si>
+  <si>
     <t>革命下のロシアで数奇な運命に翻弄された男女の死を超えた究極の愛を狂気とともに描いた怪作。</t>
   </si>
   <si>
@@ -307,6 +427,9 @@
     <t>瓶詰地獄</t>
   </si>
   <si>
+    <t>びんづめじごく</t>
+  </si>
+  <si>
     <t>無人島に漂着した兄妹が聖書を心の拠り所にしながらも抗えない罪の意識に苛まれる手記。</t>
   </si>
   <si>
@@ -316,6 +439,9 @@
     <t>陰翳礼讃</t>
   </si>
   <si>
+    <t>いんえいらいさん</t>
+  </si>
+  <si>
     <t>随筆</t>
   </si>
   <si>
@@ -328,6 +454,9 @@
     <t>渋江抽斎</t>
   </si>
   <si>
+    <t>しぶえちゅうさい</t>
+  </si>
+  <si>
     <t>江戸末期の考証学者である渋江抽斎の生涯とその家族の姿を綿密な史料調査に基づいて描く史伝。</t>
   </si>
   <si>
@@ -337,6 +466,9 @@
     <t>津軽</t>
   </si>
   <si>
+    <t>つがる</t>
+  </si>
+  <si>
     <t>故郷である津軽半島を旅しながら自身のルーツと風土そして人々との交流を温かく描いた紀行文。</t>
   </si>
   <si>
@@ -346,6 +478,9 @@
     <t>細雪（上巻）</t>
   </si>
   <si>
+    <t>ささめゆきじょうかん</t>
+  </si>
+  <si>
     <t>昭和初期の阪神間を舞台に蒔岡家の美しい四姉妹が織りなす優雅で滅びゆく日常の幕開け。</t>
   </si>
   <si>
@@ -355,6 +490,9 @@
     <t>明暗</t>
   </si>
   <si>
+    <t>めいあん</t>
+  </si>
+  <si>
     <t>自我を持て余す夫の津田と妻のお延のすれ違いを通し人間のエゴイズムを解剖した未完の絶筆。</t>
   </si>
   <si>
@@ -364,6 +502,9 @@
     <t>痴人の愛</t>
   </si>
   <si>
+    <t>ちじんのあい</t>
+  </si>
+  <si>
     <t>真面目なサラリーマンが少女ナオミを自分好みに育てようとするも逆に彼女の魔性に溺れていく。</t>
   </si>
   <si>
@@ -373,6 +514,9 @@
     <t>少将滋幹の母</t>
   </si>
   <si>
+    <t>しょうしょうしげもとのはは</t>
+  </si>
+  <si>
     <t>老いた平中と在原業平の甥である滋幹の母との悲恋を通し平安貴族の愛執と老いの悲哀を描く。</t>
   </si>
   <si>
@@ -382,6 +526,9 @@
     <t>晩年と女生徒</t>
   </si>
   <si>
+    <t>ばんねんとじょせいと</t>
+  </si>
+  <si>
     <t>ある一人の多感な女学生が朝起きてから眠るまでの日常の心の揺れ動きを独白体で綴った作品。</t>
   </si>
   <si>
@@ -391,6 +538,9 @@
     <t>冬の日</t>
   </si>
   <si>
+    <t>ふゆのひ</t>
+  </si>
+  <si>
     <t>結核の進行に怯えながら冬の太陽に自身の生命力を重ね合わせる青年の孤独と焦燥を描いた私小説。</t>
   </si>
   <si>
@@ -400,6 +550,9 @@
     <t>城のある町にて</t>
   </si>
   <si>
+    <t>しろのあるまちにて</t>
+  </si>
+  <si>
     <t>妹の療養のために訪れた城下町で自身の病と向き合いながら静かな日常の美しさを見出す物語。</t>
   </si>
   <si>
@@ -409,6 +562,9 @@
     <t>刺青</t>
   </si>
   <si>
+    <t>しせい</t>
+  </si>
+  <si>
     <t>天才的な彫り師が美しい娘の背中に巨大な女郎蜘蛛の刺青を彫り彼女の魔性を開花させる官能美。</t>
   </si>
   <si>
@@ -418,6 +574,9 @@
     <t>新生</t>
   </si>
   <si>
+    <t>しんせい</t>
+  </si>
+  <si>
     <t>姪との道外れた関係の告白と自己正当化を通して近代知識人の偽善と苦悩を赤裸々に描いた問題作。</t>
   </si>
   <si>
@@ -427,6 +586,9 @@
     <t>パノラマ島奇談</t>
   </si>
   <si>
+    <t>ぱのらまとうきだん</t>
+  </si>
+  <si>
     <t>莫大な財産を手に入れた男が孤島に理想のユートピアであるパノラマ島を建設する狂気の犯罪。</t>
   </si>
   <si>
@@ -436,6 +598,9 @@
     <t>盲目物語</t>
   </si>
   <si>
+    <t>もうもくものがたり</t>
+  </si>
+  <si>
     <t>盲目の按摩が織田信長や豊臣秀吉に翻弄されるお市の方の悲劇的な生涯を静かに語り聞かせる。</t>
   </si>
   <si>
@@ -445,6 +610,9 @@
     <t>少年探偵団</t>
   </si>
   <si>
+    <t>しょうねんたんていだん</t>
+  </si>
+  <si>
     <t>小林少年率いる少年探偵団が名探偵明智小五郎とともに怪人二十面相の悪事を阻止する冒険活劇。</t>
   </si>
   <si>
@@ -454,6 +622,9 @@
     <t>怪人二十面相</t>
   </si>
   <si>
+    <t>かいじんにじゅうめんそう</t>
+  </si>
+  <si>
     <t>変装の名手である大怪盗二十面相と名探偵明智小五郎の記念すべき初対決を描くシリーズ第一作。</t>
   </si>
   <si>
@@ -463,6 +634,9 @@
     <t>D坂の殺人事件</t>
   </si>
   <si>
+    <t>でぃーざかのさつじんじけん</t>
+  </si>
+  <si>
     <t>D坂の古本屋で起きた密室殺人事件を素人探偵の明智小五郎が心理的アプローチで解決に導く。</t>
   </si>
   <si>
@@ -472,6 +646,9 @@
     <t>二銭銅貨</t>
   </si>
   <si>
+    <t>にせんどうか</t>
+  </si>
+  <si>
     <t>二銭銅貨に隠された暗号を巡って友人同士が知恵比べを繰り広げる日本初の本格的トリック小説。</t>
   </si>
   <si>
@@ -481,6 +658,9 @@
     <t>心理試験</t>
   </si>
   <si>
+    <t>しんりしけん</t>
+  </si>
+  <si>
     <t>完全犯罪を目論んだ貧しい大学生が最新の心理試験によって明智小五郎に嘘を見破られる倒叙物。</t>
   </si>
   <si>
@@ -490,6 +670,9 @@
     <t>斜陽</t>
   </si>
   <si>
+    <t>しゃよう</t>
+  </si>
+  <si>
     <t>没落していく華族の姿を通し滅びの美学と新しい道徳観のもとで力強く生きようとする女性を描く。</t>
   </si>
   <si>
@@ -499,6 +682,9 @@
     <t>十三夜</t>
   </si>
   <si>
+    <t>じゅうさんや</t>
+  </si>
+  <si>
     <t>夫からの虐げに耐えかねて実家に戻ったお関が親に諭され再び婚家へ戻る道中での哀しい再会。</t>
   </si>
   <si>
@@ -508,6 +694,9 @@
     <t>夜叉ヶ池</t>
   </si>
   <si>
+    <t>やしゃがいけ</t>
+  </si>
+  <si>
     <t>日照りに苦しむ村人と夜叉ヶ池に封印された竜神の約束を巡る泉鏡花ならではの美しくも悲しい戯曲。</t>
   </si>
   <si>
@@ -517,6 +706,9 @@
     <t>門</t>
   </si>
   <si>
+    <t>もん</t>
+  </si>
+  <si>
     <t>親友を裏切って妻を奪った罪悪感に苛まれながらひっそりと暮らす夫婦の孤独と救済への渇望。</t>
   </si>
   <si>
@@ -526,6 +718,9 @@
     <t>大つごもり</t>
   </si>
   <si>
+    <t>おおつごもり</t>
+  </si>
+  <si>
     <t>大晦日の夜にお金に困った奉公人のお峯が主人の金庫からお金を盗んでしまうが予期せぬ結末を迎える。</t>
   </si>
   <si>
@@ -553,6 +748,9 @@
     <t>グスコーブドリの伝記</t>
   </si>
   <si>
+    <t>ぐすこーぶどりのでんき</t>
+  </si>
+  <si>
     <t>冷害に苦しむ人々を救うため自らを犠牲にして火山を爆発させるブドリの崇高な自己犠牲の物語。</t>
   </si>
   <si>
@@ -562,6 +760,9 @@
     <t>雁</t>
   </si>
   <si>
+    <t>がん</t>
+  </si>
+  <si>
     <t>高利貸しの妾となったお玉と偶然出会った医学生岡田との実ることのなかった淡く切ない恋心。</t>
   </si>
   <si>
@@ -571,6 +772,9 @@
     <t>三四郎</t>
   </si>
   <si>
+    <t>さんしろう</t>
+  </si>
+  <si>
     <t>九州から上京してきた青年三四郎が都会の空気と新しい女性の姿に戸惑いながら成長していく姿。</t>
   </si>
   <si>
@@ -580,6 +784,9 @@
     <t>光と風と夢</t>
   </si>
   <si>
+    <t>ひかりとかぜとゆめ</t>
+  </si>
+  <si>
     <t>サモア島に渡ったイギリスの作家スティーヴンソンの晩年の闘病生活と現地人との交流を描く。</t>
   </si>
   <si>
@@ -589,6 +796,9 @@
     <t>青年</t>
   </si>
   <si>
+    <t>せいねん</t>
+  </si>
+  <si>
     <t>上京したての純朴な青年純一が都会の様々な知識人や女性たちと交わりながら自己形成していく。</t>
   </si>
   <si>
@@ -607,6 +817,9 @@
     <t>芋粥</t>
   </si>
   <si>
+    <t>いもがゆ</t>
+  </si>
+  <si>
     <t>芋粥を飽きるほど食べたいという夢を持つ冴えない侍が実際にその願いを叶えられることの滑稽さ。</t>
   </si>
   <si>
@@ -616,6 +829,9 @@
     <t>少女地獄</t>
   </si>
   <si>
+    <t>しょうじょじごく</t>
+  </si>
+  <si>
     <t>虚言癖のある看護婦など三人の少女たちが自ら作り上げた地獄の中で破滅していく姿を描く書簡体。</t>
   </si>
   <si>
@@ -625,6 +841,9 @@
     <t>風の又三郎</t>
   </si>
   <si>
+    <t>かぜのまたさぶろう</t>
+  </si>
+  <si>
     <t>風の強い日に転校してきた不思議な少年と村の子供たちの間で織りなされるひと夏の幻想的な交流。</t>
   </si>
   <si>
@@ -634,6 +853,9 @@
     <t>うたかたの記</t>
   </si>
   <si>
+    <t>うたかたのき</t>
+  </si>
+  <si>
     <t>ミュンヘンに留学した画学生がモデルの狂気の少女と哀しくも美しい交流を持つが悲劇的な結末を迎える。</t>
   </si>
   <si>
@@ -643,6 +865,9 @@
     <t>お伽草紙</t>
   </si>
   <si>
+    <t>おとぎぞうし</t>
+  </si>
+  <si>
     <t>防空壕の中で父親が子供に語って聞かせる日本の昔話を太宰治独自のユーモアと解釈で再構築した作品。</t>
   </si>
   <si>
@@ -652,6 +877,9 @@
     <t>櫻の樹の下には</t>
   </si>
   <si>
+    <t>さくらのきのしたには</t>
+  </si>
+  <si>
     <t>桜の木の美しさの根源には死体が埋まっているのだという倒錯した幻想美を鮮烈な詩的言語で表現。</t>
   </si>
   <si>
@@ -661,6 +889,9 @@
     <t>グッド・バイ</t>
   </si>
   <si>
+    <t>ぐっどばい</t>
+  </si>
+  <si>
     <t>愛人たちとの関係を清算しようとする男が絶世の美女を偽の妻に仕立てて別れを告げて回る未完の喜劇。</t>
   </si>
   <si>
@@ -670,6 +901,9 @@
     <t>藪の中</t>
   </si>
   <si>
+    <t>やぶのなか</t>
+  </si>
+  <si>
     <t>竹藪で起きた殺人事件の真相を巡り関係者たちの証言が真っ向から食い違う人間のエゴと真実の曖昧さ。</t>
   </si>
   <si>
@@ -679,6 +913,9 @@
     <t>ヴィヨンの妻</t>
   </si>
   <si>
+    <t>ゔぃよんのつま</t>
+  </si>
+  <si>
     <t>放蕩を尽くす詩人の夫に翻弄されながらも逞しく生き抜こうとする妻の姿を通して退廃の美学を描く。</t>
   </si>
   <si>
@@ -688,6 +925,9 @@
     <t>鼻</t>
   </si>
   <si>
+    <t>はな</t>
+  </si>
+  <si>
     <t>巨大な鼻にコンプレックスを持つ僧侶が鼻を短くすることに成功するが周囲の嘲笑の質が変化して苦悩する。</t>
   </si>
   <si>
@@ -697,6 +937,9 @@
     <t>草枕</t>
   </si>
   <si>
+    <t>くさまくら</t>
+  </si>
+  <si>
     <t>山村の温泉宿を訪れた画工が非人情の世界を求めて俗世を離れ美しい那美という女性に出会う。</t>
   </si>
   <si>
@@ -706,6 +949,9 @@
     <t>坊っちゃん</t>
   </si>
   <si>
+    <t>ぼっちゃん</t>
+  </si>
+  <si>
     <t>無鉄砲で正義感の強い江戸っ子の坊っちゃんが四国の中学校の教師となり偽善的な同僚たちと衝突する。</t>
   </si>
   <si>
@@ -715,6 +961,9 @@
     <t>ドグラ・マグラ</t>
   </si>
   <si>
+    <t>どぐらまぐら</t>
+  </si>
+  <si>
     <t>記憶喪失の青年が精神科病棟で目覚め自己のアイデンティティと数奇な因縁を探求する奇書。</t>
   </si>
   <si>
@@ -724,6 +973,9 @@
     <t>春と修羅</t>
   </si>
   <si>
+    <t>はるとしゅら</t>
+  </si>
+  <si>
     <t>宇宙的な広がりと仏教的死生観を背景に自身を修羅と位置づけた宮沢賢治の魂の軌跡を綴った詩集。</t>
   </si>
   <si>
@@ -733,6 +985,9 @@
     <t>彼岸過迄</t>
   </si>
   <si>
+    <t>ひがんすぎまで</t>
+  </si>
+  <si>
     <t>人間の自意識の過剰さとそれゆえの孤独や苦悩をいくつかの短編を連ねたオムニバス形式で深く追求する。</t>
   </si>
   <si>
@@ -742,6 +997,9 @@
     <t>高瀬舟</t>
   </si>
   <si>
+    <t>たかせぶね</t>
+  </si>
+  <si>
     <t>弟を殺した罪で高瀬舟に乗せられた喜助の清らかな心を通して安楽死と人間の欲望について問いかける。</t>
   </si>
   <si>
@@ -751,6 +1009,9 @@
     <t>河童</t>
   </si>
   <si>
+    <t>かっぱ</t>
+  </si>
+  <si>
     <t>精神病患者の告白という体裁で河童の国での奇妙な体験を語り人間社会の常識や道徳を鋭く風刺する。</t>
   </si>
   <si>
@@ -760,6 +1021,9 @@
     <t>李陵</t>
   </si>
   <si>
+    <t>りりょう</t>
+  </si>
+  <si>
     <t>漢の武将李陵と歴史家司馬遷の運命を通し国家と個人の相克や運命に翻弄される人間の尊厳を描く。</t>
   </si>
   <si>
@@ -778,6 +1042,9 @@
     <t>オツベルと象</t>
   </si>
   <si>
+    <t>おつべるとぞう</t>
+  </si>
+  <si>
     <t>強欲な地主オツベルに騙されて酷使される白い象が仲間の象たちに助け出される痛快で教訓的な物語。</t>
   </si>
   <si>
@@ -787,6 +1054,9 @@
     <t>蜘蛛の糸</t>
   </si>
   <si>
+    <t>くものいと</t>
+  </si>
+  <si>
     <t>地獄の底で苦しむ大泥棒の犍陀多が御釈迦様から垂らされた一本の蜘蛛の糸を登ろうとするがエゴにより堕ちる。</t>
   </si>
   <si>
@@ -796,6 +1066,9 @@
     <t>人間失格</t>
   </si>
   <si>
+    <t>にんげんしっかく</t>
+  </si>
+  <si>
     <t>他者との心の交流に絶望し道化を演じながらも破滅的な生活へと堕ちていく葉蔵の手記を通した自己否定の記録。</t>
   </si>
   <si>
@@ -805,6 +1078,9 @@
     <t>地獄変</t>
   </si>
   <si>
+    <t>じごくへん</t>
+  </si>
+  <si>
     <t>芸術至上主義の絵師良秀が地獄屏風を完成させるため実の娘が火あぶりにされる様を恍惚と見つめる。</t>
   </si>
   <si>
@@ -814,6 +1090,9 @@
     <t>夜明け前（第一部上）</t>
   </si>
   <si>
+    <t>よあけまえだいいちぶじょう</t>
+  </si>
+  <si>
     <t>幕末の木曾馬籠宿を舞台に国学に傾倒する青山半蔵が時代の激しい変化の波に翻弄され始める第一部の上巻。</t>
   </si>
   <si>
@@ -823,6 +1102,9 @@
     <t>家（下）</t>
   </si>
   <si>
+    <t>いえげ</t>
+  </si>
+  <si>
     <t>旧家の因習と近代的な自我との間で葛藤し没落していく二つの家族の姿を自然主義的手法で描いた完結編。</t>
   </si>
   <si>
@@ -832,6 +1114,9 @@
     <t>家（上）</t>
   </si>
   <si>
+    <t>いえじょう</t>
+  </si>
+  <si>
     <t>封建的な家族制度の重圧のなかで苦悩する青年たちの姿を通し明治期の旧家が崩壊していく過程を描く上巻。</t>
   </si>
   <si>
@@ -850,6 +1135,9 @@
     <t>夜明け前（第一部下）</t>
   </si>
   <si>
+    <t>よあけまえだいいちぶげ</t>
+  </si>
+  <si>
     <t>明治維新の動乱が木曾の山村にも波及し青山半蔵の理想と現実のズレが次第に大きくなっていく第一部の下巻。</t>
   </si>
   <si>
@@ -859,6 +1147,9 @@
     <t>夜明け前（第二部上）</t>
   </si>
   <si>
+    <t>よあけまえだいにぶじょう</t>
+  </si>
+  <si>
     <t>維新後の新しい時代が到来するも青山半蔵の純粋な理想は国政の現実と衝突し深い孤独へと向かう第二部の上巻。</t>
   </si>
   <si>
@@ -868,6 +1159,9 @@
     <t>セロ弾きのゴーシュ</t>
   </si>
   <si>
+    <t>せろひきのごーしゅ</t>
+  </si>
+  <si>
     <t>楽団でいつも怒られている不器用なチェロ弾きのゴーシュが動物たちとの交流を通して音楽の真髄に触れ成長する。</t>
   </si>
   <si>
@@ -877,6 +1171,9 @@
     <t>破戒</t>
   </si>
   <si>
+    <t>はかい</t>
+  </si>
+  <si>
     <t>被差別部落出身であることを隠して生きる青年教師の瀬川丑松が身分を告白し自己解放を遂げるまでの社会的苦悩。</t>
   </si>
   <si>
@@ -886,6 +1183,9 @@
     <t>天守物語</t>
   </si>
   <si>
+    <t>てんしゅものがたり</t>
+  </si>
+  <si>
     <t>白鷺城の天守閣に住む異形の姫君と人間の若武者との種族を超えた純粋で美しい愛を描いた幻想的な戯曲。</t>
   </si>
   <si>
@@ -895,6 +1195,9 @@
     <t>山椒大夫</t>
   </si>
   <si>
+    <t>さんしょうだゆう</t>
+  </si>
+  <si>
     <t>人買いに売られ奴隷となった安寿と厨子王の姉弟の悲劇と弟の出世による母との再会を格調高く描いた歴史小説。</t>
   </si>
   <si>
@@ -904,6 +1207,9 @@
     <t>阿部一族</t>
   </si>
   <si>
+    <t>あべいちぞく</t>
+  </si>
+  <si>
     <t>主君の死に際して殉死を許されなかった阿部一族が名誉を守るために反逆へと至る武士道の美学と悲劇。</t>
   </si>
   <si>
@@ -913,6 +1219,9 @@
     <t>ヰタ・セクスアリス</t>
   </si>
   <si>
+    <t>ゐたせくすありす</t>
+  </si>
+  <si>
     <t>自身の性的な目覚めと経験を客観的かつ冷静な筆致で振り返り自然主義文学の肉欲偏重に異議を唱えた作品。</t>
   </si>
   <si>
@@ -922,6 +1231,9 @@
     <t>或阿呆の一生</t>
   </si>
   <si>
+    <t>あるあほうのいっしょう</t>
+  </si>
+  <si>
     <t>芥川自身の精神的危機と狂気への恐怖を断片的な五十余りのエピソードで構成した痛切な自伝的遺稿。</t>
   </si>
   <si>
@@ -931,6 +1243,9 @@
     <t>歌行燈</t>
   </si>
   <si>
+    <t>うたあんどん</t>
+  </si>
+  <si>
     <t>能楽師の青年が桑名の地で過去の過ちと向き合い芸の真髄を開眼するまでを幽玄の美をもって描いた名作。</t>
   </si>
   <si>
@@ -940,6 +1255,9 @@
     <t>注文の多い料理店</t>
   </si>
   <si>
+    <t>ちゅうもんのおおいりょうりてん</t>
+  </si>
+  <si>
     <t>山で迷った二人の紳士が山猫亭というレストランに入り数々の奇妙な注文を受けるうちに自らが食べられる危機に陥る。</t>
   </si>
   <si>
@@ -949,6 +1267,9 @@
     <t>どんぐりと山猫</t>
   </si>
   <si>
+    <t>どんぐりとやまねこ</t>
+  </si>
+  <si>
     <t>山猫から裁判長に任命された一郎が誰がいちばん偉いかで争うどんぐりたちを見事に裁くユーモラスな童話。</t>
   </si>
   <si>
@@ -958,6 +1279,9 @@
     <t>弟子</t>
   </si>
   <si>
+    <t>でし</t>
+  </si>
+  <si>
     <t>孔子の愛弟子である子路の豪傑でありながらも純粋で真っ直ぐな生き様と悲劇的な最期を描いた歴史小説。</t>
   </si>
   <si>
@@ -967,6 +1291,9 @@
     <t>晩年に就いて</t>
   </si>
   <si>
+    <t>ばんねんについて</t>
+  </si>
+  <si>
     <t>処女短編集のタイトルに込めた思いや自身の文学観について語った太宰の屈折した自意識が窺えるエッセイ。</t>
   </si>
   <si>
@@ -976,6 +1303,9 @@
     <t>歯車</t>
   </si>
   <si>
+    <t>はぐるま</t>
+  </si>
+  <si>
     <t>幻視する半透明の歯車に怯え精神の崩壊と死への恐怖に苛まれる芥川の最晩年の極限の心理状態を描く。</t>
   </si>
   <si>
@@ -985,6 +1315,9 @@
     <t>行人</t>
   </si>
   <si>
+    <t>こうじん</t>
+  </si>
+  <si>
     <t>妻への猜疑心から精神を病んでいく兄と彼を見守る弟の目を通して人間の絶対的な孤独と狂気を鋭く描破した。</t>
   </si>
   <si>
@@ -994,6 +1327,9 @@
     <t>枯野抄</t>
   </si>
   <si>
+    <t>かれのしょう</t>
+  </si>
+  <si>
     <t>松尾芭蕉の死の床を囲む弟子たちの複雑な心理や利己的な打算を浮き彫りにし人間のエゴイズムを冷徹に描く。</t>
   </si>
   <si>
@@ -1003,6 +1339,9 @@
     <t>桜桃</t>
   </si>
   <si>
+    <t>おうとう</t>
+  </si>
+  <si>
     <t>家庭を顧みず酒に逃避する父親の弱さと苦悩を桜桃の実の美しさと対比させながら哀切に描いた私小説。</t>
   </si>
   <si>
@@ -1012,6 +1351,9 @@
     <t>名人伝</t>
   </si>
   <si>
+    <t>めいじんでん</t>
+  </si>
+  <si>
     <t>弓の道を極めようとした男が最終的に弓の存在すら忘れるという無為自然の境地に達する老荘思想を体現した奇譚。</t>
   </si>
   <si>
@@ -1021,6 +1363,9 @@
     <t>交尾</t>
   </si>
   <si>
+    <t>こうび</t>
+  </si>
+  <si>
     <t>生物の交尾行動という本能的な営みを執拗なまでの客観描写で捉え独自の死生観やエロティシズムを表現した異色作。</t>
   </si>
   <si>
@@ -1030,9 +1375,15 @@
     <t>少女病</t>
   </si>
   <si>
+    <t>しょうじょびょう</t>
+  </si>
+  <si>
     <t>田山花袋</t>
   </si>
   <si>
+    <t>たやまかたい</t>
+  </si>
+  <si>
     <t>電車で見かける少女たちに異常な執着を抱く中年の小説家の病的な心理を描写した自然主義文学の先駆的作品。</t>
   </si>
   <si>
@@ -1042,6 +1393,9 @@
     <t>夢十夜</t>
   </si>
   <si>
+    <t>ゆめじゅうや</t>
+  </si>
+  <si>
     <t>こんな夢を見たという書き出しから始まる十の幻想的でシュールな夢の記録を通して深層心理を鮮烈に描く。</t>
   </si>
   <si>
@@ -1051,9 +1405,15 @@
     <t>小公女</t>
   </si>
   <si>
+    <t>しょうこうじょ</t>
+  </si>
+  <si>
     <t>フランシス・ホジソン・バーネット</t>
   </si>
   <si>
+    <t>ふらんしすほじそんばーねっと</t>
+  </si>
+  <si>
     <t>裕福な少女セーラが父親の死により過酷な運命に突き落とされるも高貴な心を失わず逆境を生き抜く感動の物語。</t>
   </si>
   <si>
@@ -1063,6 +1423,9 @@
     <t>外科室</t>
   </si>
   <si>
+    <t>げかしつ</t>
+  </si>
+  <si>
     <t>麻酔を拒否して手術を受ける伯爵夫人と執刀医との間に隠された過去の悲恋と究極の純愛を描いた浪漫主義の傑作。</t>
   </si>
   <si>
@@ -1072,9 +1435,15 @@
     <t>野菊の墓</t>
   </si>
   <si>
+    <t>のぎくのはか</t>
+  </si>
+  <si>
     <t>伊藤左千夫</t>
   </si>
   <si>
+    <t>いとうさちお</t>
+  </si>
+  <si>
     <t>十五歳の少年政夫と二歳年上の従姉民子との美しくも悲しい初恋の破局を野菊の可憐な姿に重ね合わせて描く。</t>
   </si>
   <si>
@@ -1084,9 +1453,15 @@
     <t>ごん狐</t>
   </si>
   <si>
+    <t>ごんぎつね</t>
+  </si>
+  <si>
     <t>新美南吉</t>
   </si>
   <si>
+    <t>にいみなんきち</t>
+  </si>
+  <si>
     <t>いたずら狐のごんが罪滅ぼしのために栗や松茸を届けるも猟師の兵十に誤解されて撃たれてしまう哀しい結末。</t>
   </si>
   <si>
@@ -1096,6 +1471,9 @@
     <t>堕落論</t>
   </si>
   <si>
+    <t>だらくろん</t>
+  </si>
+  <si>
     <t>敗戦直後の日本において既存の道徳や権威からの解放と真の人間性の回復のためには正しく堕落すべきだと説く。</t>
   </si>
   <si>
@@ -1105,6 +1483,9 @@
     <t>手袋を買いに</t>
   </si>
   <si>
+    <t>てぶくろをかいに</t>
+  </si>
+  <si>
     <t>冷たい雪の日に子狐に手袋を買ってやりたいと願う母狐の深い愛情と人間への信頼を描いた心温まる童話。</t>
   </si>
   <si>
@@ -1114,6 +1495,9 @@
     <t>最後の一句</t>
   </si>
   <si>
+    <t>さいごのいっく</t>
+  </si>
+  <si>
     <t>死刑宣告を受けた父親を救うため幼い娘がいちという驚くべき決断を役人に申し出る自己犠牲と強い意志の物語。</t>
   </si>
   <si>
@@ -1123,6 +1507,9 @@
     <t>女生徒</t>
   </si>
   <si>
+    <t>じょせいと</t>
+  </si>
+  <si>
     <t>女学生の一日の生活の心の動きを瑞々しく繊細な語り口で捉え思春期特有の憂鬱と希望を見事に表現した。</t>
   </si>
   <si>
@@ -1132,9 +1519,15 @@
     <t>山羊の歌</t>
   </si>
   <si>
+    <t>やぎのうた</t>
+  </si>
+  <si>
     <t>中原中也</t>
   </si>
   <si>
+    <t>なかはらちゅうや</t>
+  </si>
+  <si>
     <t>喪失感や悲哀を音楽的なリズムと独特の叙情性で歌い上げた中原中也の第一詩集であり近代詩の金字塔。</t>
   </si>
   <si>
@@ -1144,6 +1537,9 @@
     <t>在りし日の歌</t>
   </si>
   <si>
+    <t>ありしひのうた</t>
+  </si>
+  <si>
     <t>亡き子への哀悼や迫り来る死への予感の中で魂の叫びと純粋な祈りを透明感のある言葉で紡いだ死後の詩集。</t>
   </si>
   <si>
@@ -1153,9 +1549,15 @@
     <t>萱草に寄す</t>
   </si>
   <si>
+    <t>わすれぐさによす</t>
+  </si>
+  <si>
     <t>立原道造</t>
   </si>
   <si>
+    <t>たちはらみちぞう</t>
+  </si>
+  <si>
     <t>繊細な感性と建築的な構成美を併せ持つ詩人が夭折する前に遺した叙情溢れるソネット形式の詩の数々。</t>
   </si>
   <si>
@@ -1165,6 +1567,9 @@
     <t>暁と夕の詩</t>
   </si>
   <si>
+    <t>あかつきとゆうべのし</t>
+  </si>
+  <si>
     <t>軽井沢の自然の中で生の輝きと死の影を見つめながら美しい音楽の調べのように奏でられた立原道造の詩集。</t>
   </si>
   <si>
@@ -1174,6 +1579,9 @@
     <t>夜行巡査</t>
   </si>
   <si>
+    <t>やこうじゅんさ</t>
+  </si>
+  <si>
     <t>職務に忠実なあまり恋人の叔父を逮捕してしまう巡査の悲劇を通して義理と人情の板挟みになる苦悩を描く。</t>
   </si>
   <si>
@@ -1183,9 +1591,15 @@
     <t>生れ出づる悩み</t>
   </si>
   <si>
+    <t>うまれいづるなやみ</t>
+  </si>
+  <si>
     <t>有島武郎</t>
   </si>
   <si>
+    <t>ありしまたけお</t>
+  </si>
+  <si>
     <t>過酷な漁夫の労働に従事しながらも画家への夢を捨てきれない青年の深い苦悩と芸術への渇望を描く。</t>
   </si>
   <si>
@@ -1195,9 +1609,15 @@
     <t>天衣無縫</t>
   </si>
   <si>
+    <t>てんいむほう</t>
+  </si>
+  <si>
     <t>織田作之助</t>
   </si>
   <si>
+    <t>おださくのすけ</t>
+  </si>
+  <si>
     <t>自由奔放で無頼な生き方をする主人公の姿を通し世間の常識に囚われない人間の真のあり方をユーモラスに探る。</t>
   </si>
   <si>
@@ -1207,6 +1627,9 @@
     <t>トロッコ</t>
   </si>
   <si>
+    <t>とろっこ</t>
+  </si>
+  <si>
     <t>土工と一緒にトロッコを押して遠くまで来てしまった少年の帰り道の孤独と不安を見事な心理描写で切り取った名作。</t>
   </si>
   <si>
@@ -1216,9 +1639,15 @@
     <t>学問のすゝめ</t>
   </si>
   <si>
+    <t>がくもんのすすめ</t>
+  </si>
+  <si>
     <t>福沢諭吉</t>
   </si>
   <si>
+    <t>ふくざわゆきち</t>
+  </si>
+  <si>
     <t>天は人の上に人を造らずという言葉で始まり近代国家における個人の独立と実学の重要性を説いた啓蒙書。</t>
   </si>
   <si>
@@ -1228,6 +1657,9 @@
     <t>夫婦善哉</t>
   </si>
   <si>
+    <t>めおとぜんざい</t>
+  </si>
+  <si>
     <t>甲斐性なしの柳吉と彼に尽くすしっかり者の芸者蝶子の腐れ縁の愛の形を大阪の風土とともに活写した傑作。</t>
   </si>
   <si>
@@ -1237,6 +1669,9 @@
     <t>一房の葡萄</t>
   </si>
   <si>
+    <t>ひとふさのぶどう</t>
+  </si>
+  <si>
     <t>絵の具を盗んでしまった少年の罪悪感と彼を優しく包み込んで許す若い女性教師の温かい愛情を描く小品。</t>
   </si>
   <si>
@@ -1246,6 +1681,9 @@
     <t>杜子春</t>
   </si>
   <si>
+    <t>とししゅん</t>
+  </si>
+  <si>
     <t>仙人を目指す若者が様々な試練を受ける中で人間にとって最も大切なのは親を思う純粋な愛情だと気付く物語。</t>
   </si>
   <si>
@@ -1255,9 +1693,15 @@
     <t>草木塔</t>
   </si>
   <si>
+    <t>そうもくとう</t>
+  </si>
+  <si>
     <t>種田山頭火</t>
   </si>
   <si>
+    <t>たねださんとうか</t>
+  </si>
+  <si>
     <t>自由律俳句を提唱し漂泊の旅を続けた種田山頭火の孤独や自然との一体感を詠んだ魂の叫びともいえる句集。</t>
   </si>
   <si>
@@ -1267,9 +1711,15 @@
     <t>武蔵野</t>
   </si>
   <si>
+    <t>むさしの</t>
+  </si>
+  <si>
     <t>国木田独歩</t>
   </si>
   <si>
+    <t>くにきだどっぽ</t>
+  </si>
+  <si>
     <t>失われゆく武蔵野の雑木林の自然美とそこに暮らす人々の情景を詩情豊かに綴ったロマンティシズム溢れる名作。</t>
   </si>
   <si>
@@ -1279,9 +1729,15 @@
     <t>恩讐の彼方に</t>
   </si>
   <si>
+    <t>おんしゅうのかなたに</t>
+  </si>
+  <si>
     <t>菊池寛</t>
   </si>
   <si>
+    <t>きくちひろし</t>
+  </si>
+  <si>
     <t>主君を殺した罪滅ぼしのために洞門を掘り続ける男と彼を仇と狙う若者がやがて協力し合う感動の人間ドラマ。</t>
   </si>
   <si>
@@ -1291,9 +1747,15 @@
     <t>みだれ髪</t>
   </si>
   <si>
+    <t>みだれがみ</t>
+  </si>
+  <si>
     <t>与謝野晶子</t>
   </si>
   <si>
+    <t>よさのあきこ</t>
+  </si>
+  <si>
     <t>女性の官能や自我を力強く肯定し伝統的な和歌の殻を打ち破った浪漫主義の情熱的で革命的な歌集。</t>
   </si>
   <si>
@@ -1303,9 +1765,15 @@
     <t>今戸心中</t>
   </si>
   <si>
+    <t>いまどしんじゅう</t>
+  </si>
+  <si>
     <t>広津柳浪</t>
   </si>
   <si>
+    <t>ひろつりゅうろう</t>
+  </si>
+  <si>
     <t>社会の底辺に生きる醜い女と冴えない男が世間から冷遇された末に迎える哀れな心中の結末を深刻小説として描く。</t>
   </si>
   <si>
@@ -1315,6 +1783,9 @@
     <t>蒲団</t>
   </si>
   <si>
+    <t>ふとん</t>
+  </si>
+  <si>
     <t>中年作家が同居する美貌の女弟子に対して抱く醜い肉欲と嫉妬を赤裸々に告白し自然主義文学の端緒を開いた。</t>
   </si>
   <si>
@@ -1324,9 +1795,15 @@
     <t>浮雲</t>
   </si>
   <si>
+    <t>うきぐも</t>
+  </si>
+  <si>
     <t>二葉亭四迷</t>
   </si>
   <si>
+    <t>ふたばていしめい</t>
+  </si>
+  <si>
     <t>文明開化の世に馴染めない生真面目な内海文三の挫折と孤独を通し日本における近代的な自我の芽生えを描いた。</t>
   </si>
   <si>
@@ -1336,6 +1813,9 @@
     <t>不連続殺人事件</t>
   </si>
   <si>
+    <t>ふれんぞくさつじんじけん</t>
+  </si>
+  <si>
     <t>戦後の荒廃した山奥の邸宅で次々と起こる見立て殺人を冷徹な論理で解き明かす本格ミステリーの金字塔。</t>
   </si>
   <si>
@@ -1345,9 +1825,15 @@
     <t>黒死館殺人事件</t>
   </si>
   <si>
+    <t>こくしかんさつじんじけん</t>
+  </si>
+  <si>
     <t>小栗虫太郎</t>
   </si>
   <si>
+    <t>おぐりむしたろう</t>
+  </si>
+  <si>
     <t>オカルティズムやペダントリーに満ちた異様な館で起こる連続殺人を法水麟太郎が独自の衒学趣味で解決する奇書。</t>
   </si>
   <si>
@@ -1357,7 +1843,13 @@
     <t>金色夜叉</t>
   </si>
   <si>
+    <t>こんじきやしゃ</t>
+  </si>
+  <si>
     <t>尾崎紅葉</t>
+  </si>
+  <si>
+    <t>おざきこうよう</t>
   </si>
   <si>
     <t>金のために裏切ったお宮への復讐を誓い冷酷な高利貸しとなった間貫一の愛憎と苦悩を描く明治の代表的悲恋小説。</t>
@@ -1640,3133 +2132,3955 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1">
         <v>85.0</v>
       </c>
-      <c r="E2" s="1">
+      <c r="G2" s="1">
         <v>1925.0</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1">
         <v>95.0</v>
       </c>
-      <c r="E3" s="1">
+      <c r="G3" s="1">
         <v>1934.0</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>16</v>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1">
+        <v>25</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="1">
         <v>98.0</v>
       </c>
-      <c r="E4" s="1">
+      <c r="G4" s="1">
         <v>1905.0</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>20</v>
+      <c r="H4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="1">
+        <v>31</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="1">
         <v>98.0</v>
       </c>
-      <c r="E5" s="1">
+      <c r="G5" s="1">
         <v>1940.0</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>24</v>
+      <c r="H5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="1">
+        <v>37</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="1">
         <v>95.0</v>
       </c>
-      <c r="E6" s="1">
+      <c r="G6" s="1">
         <v>1915.0</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>28</v>
+      <c r="H6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="1">
+        <v>43</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="1">
         <v>90.0</v>
       </c>
-      <c r="E7" s="1">
+      <c r="G7" s="1">
         <v>1890.0</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>32</v>
+      <c r="H7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="1">
+        <v>49</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="1">
         <v>80.0</v>
       </c>
-      <c r="E8" s="1">
+      <c r="G8" s="1">
         <v>1925.0</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>37</v>
+      <c r="H8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="1">
+        <v>56</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="1">
         <v>75.0</v>
       </c>
-      <c r="E9" s="1">
+      <c r="G9" s="1">
         <v>1900.0</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>41</v>
+      <c r="H9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="1">
+        <v>62</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="1">
         <v>85.0</v>
       </c>
-      <c r="E10" s="1">
+      <c r="G10" s="1">
         <v>1947.0</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>45</v>
+      <c r="H10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="1">
+        <v>68</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="1">
         <v>95.0</v>
       </c>
-      <c r="E11" s="1">
+      <c r="G11" s="1">
         <v>1942.0</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>49</v>
+      <c r="H11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="1">
+        <v>74</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="1">
         <v>80.0</v>
       </c>
-      <c r="E12" s="1">
+      <c r="G12" s="1">
         <v>1935.0</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>53</v>
+      <c r="H12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="1">
+        <v>80</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="1">
         <v>75.0</v>
       </c>
-      <c r="E13" s="1">
+      <c r="G13" s="1">
         <v>1914.0</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>56</v>
+      <c r="H13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="1">
+        <v>84</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="1">
         <v>80.0</v>
       </c>
-      <c r="E14" s="1">
+      <c r="G14" s="1">
         <v>1931.0</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>60</v>
+      <c r="H14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="1">
+        <v>90</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="1">
         <v>90.0</v>
       </c>
-      <c r="E15" s="1">
+      <c r="G15" s="1">
         <v>1921.0</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>63</v>
+      <c r="H15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="1">
+        <v>94</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="1">
         <v>80.0</v>
       </c>
-      <c r="E16" s="1">
+      <c r="G16" s="1">
         <v>1928.0</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>66</v>
+      <c r="H16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="1">
+        <v>98</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="1">
         <v>85.0</v>
       </c>
-      <c r="E17" s="1">
+      <c r="G17" s="1">
         <v>1930.0</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>69</v>
+      <c r="H17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="1">
+        <v>102</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" s="1">
         <v>88.0</v>
       </c>
-      <c r="E18" s="1">
+      <c r="G18" s="1">
         <v>1948.0</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>72</v>
+      <c r="H18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="1">
+        <v>106</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="1">
         <v>80.0</v>
       </c>
-      <c r="E19" s="1">
+      <c r="G19" s="1">
         <v>1936.0</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>75</v>
+      <c r="H19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="1">
+        <v>110</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="1">
         <v>85.0</v>
       </c>
-      <c r="E20" s="1">
+      <c r="G20" s="1">
         <v>1939.0</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>78</v>
+      <c r="H20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="1">
+        <v>114</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" s="1">
         <v>90.0</v>
       </c>
-      <c r="E21" s="1">
+      <c r="G21" s="1">
         <v>1933.0</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>81</v>
+      <c r="H21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="1">
+        <v>118</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F22" s="1">
         <v>88.0</v>
       </c>
-      <c r="E22" s="1">
+      <c r="G22" s="1">
         <v>1948.0</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>84</v>
+      <c r="H22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="1">
+      <c r="F23" s="1">
         <v>82.0</v>
       </c>
-      <c r="E23" s="1">
+      <c r="G23" s="1">
         <v>1929.0</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>87</v>
+      <c r="H23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" s="1">
+        <v>126</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" s="1">
         <v>70.0</v>
       </c>
-      <c r="E24" s="1">
+      <c r="G24" s="1">
         <v>1894.0</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>91</v>
+      <c r="H24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" s="1">
+        <v>132</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25" s="1">
         <v>75.0</v>
       </c>
-      <c r="E25" s="1">
+      <c r="G25" s="1">
         <v>1928.0</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>95</v>
+      <c r="H25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" s="1">
+        <v>138</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" s="1">
         <v>80.0</v>
       </c>
-      <c r="E26" s="1">
+      <c r="G26" s="1">
         <v>1928.0</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>98</v>
+      <c r="H26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="1">
+        <v>142</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F27" s="1">
         <v>85.0</v>
       </c>
-      <c r="E27" s="1">
+      <c r="G27" s="1">
         <v>1933.0</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>102</v>
+      <c r="H27" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="1">
+        <v>147</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" s="1">
         <v>75.0</v>
       </c>
-      <c r="E28" s="1">
+      <c r="G28" s="1">
         <v>1916.0</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>105</v>
+      <c r="H28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="1">
+        <v>151</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" s="1">
         <v>85.0</v>
       </c>
-      <c r="E29" s="1">
+      <c r="G29" s="1">
         <v>1944.0</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>108</v>
+      <c r="H29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="1">
+        <v>155</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F30" s="1">
         <v>88.0</v>
       </c>
-      <c r="E30" s="1">
+      <c r="G30" s="1">
         <v>1948.0</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>111</v>
+      <c r="H30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="1">
+        <v>159</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="1">
         <v>92.0</v>
       </c>
-      <c r="E31" s="1">
+      <c r="G31" s="1">
         <v>1916.0</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>114</v>
+      <c r="H31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>115</v>
+        <v>161</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D32" s="1">
+        <v>163</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32" s="1">
         <v>90.0</v>
       </c>
-      <c r="E32" s="1">
+      <c r="G32" s="1">
         <v>1924.0</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>117</v>
+      <c r="H32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" s="1">
+        <v>167</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F33" s="1">
         <v>80.0</v>
       </c>
-      <c r="E33" s="1">
+      <c r="G33" s="1">
         <v>1950.0</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>120</v>
+      <c r="H33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D34" s="1">
+        <v>171</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" s="1">
         <v>85.0</v>
       </c>
-      <c r="E34" s="1">
+      <c r="G34" s="1">
         <v>1939.0</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>123</v>
+      <c r="H34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>124</v>
+        <v>173</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>125</v>
+        <v>174</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="1">
+        <v>175</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="1">
         <v>75.0</v>
       </c>
-      <c r="E35" s="1">
+      <c r="G35" s="1">
         <v>1927.0</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>126</v>
+      <c r="H35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>128</v>
+        <v>178</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="1">
+        <v>179</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="1">
         <v>70.0</v>
       </c>
-      <c r="E36" s="1">
+      <c r="G36" s="1">
         <v>1925.0</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>129</v>
+      <c r="H36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>130</v>
+        <v>181</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>131</v>
+        <v>182</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D37" s="1">
+        <v>183</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F37" s="1">
         <v>85.0</v>
       </c>
-      <c r="E37" s="1">
+      <c r="G37" s="1">
         <v>1910.0</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>132</v>
+      <c r="H37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" s="1">
+        <v>187</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="1">
         <v>80.0</v>
       </c>
-      <c r="E38" s="1">
+      <c r="G38" s="1">
         <v>1919.0</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>135</v>
+      <c r="H38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>136</v>
+        <v>189</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>137</v>
+        <v>190</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="1">
+        <v>191</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F39" s="1">
         <v>85.0</v>
       </c>
-      <c r="E39" s="1">
+      <c r="G39" s="1">
         <v>1926.0</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>138</v>
+      <c r="H39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D40" s="1">
+        <v>195</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F40" s="1">
         <v>80.0</v>
       </c>
-      <c r="E40" s="1">
+      <c r="G40" s="1">
         <v>1931.0</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>141</v>
+      <c r="H40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>142</v>
+        <v>197</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>143</v>
+        <v>198</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D41" s="1">
+        <v>199</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F41" s="1">
         <v>90.0</v>
       </c>
-      <c r="E41" s="1">
+      <c r="G41" s="1">
         <v>1937.0</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>144</v>
+      <c r="H41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>145</v>
+        <v>201</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D42" s="1">
+        <v>203</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F42" s="1">
         <v>92.0</v>
       </c>
-      <c r="E42" s="1">
+      <c r="G42" s="1">
         <v>1936.0</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>147</v>
+      <c r="H42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>148</v>
+        <v>205</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>149</v>
+        <v>206</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D43" s="1">
+        <v>207</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F43" s="1">
         <v>88.0</v>
       </c>
-      <c r="E43" s="1">
+      <c r="G43" s="1">
         <v>1925.0</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>150</v>
+      <c r="H43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D44" s="1">
+        <v>211</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F44" s="1">
         <v>80.0</v>
       </c>
-      <c r="E44" s="1">
+      <c r="G44" s="1">
         <v>1923.0</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>153</v>
+      <c r="H44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>155</v>
+        <v>214</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D45" s="1">
+        <v>215</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F45" s="1">
         <v>75.0</v>
       </c>
-      <c r="E45" s="1">
+      <c r="G45" s="1">
         <v>1925.0</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>156</v>
+      <c r="H45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>157</v>
+        <v>217</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>158</v>
+        <v>218</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D46" s="1">
+        <v>219</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F46" s="1">
         <v>95.0</v>
       </c>
-      <c r="E46" s="1">
+      <c r="G46" s="1">
         <v>1947.0</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>159</v>
+      <c r="H46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>160</v>
+        <v>221</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>161</v>
+        <v>222</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D47" s="1">
+        <v>223</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47" s="1">
         <v>85.0</v>
       </c>
-      <c r="E47" s="1">
+      <c r="G47" s="1">
         <v>1895.0</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>162</v>
+      <c r="H47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>163</v>
+        <v>225</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>164</v>
+        <v>226</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D48" s="1">
+        <v>227</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F48" s="1">
         <v>80.0</v>
       </c>
-      <c r="E48" s="1">
+      <c r="G48" s="1">
         <v>1913.0</v>
       </c>
-      <c r="F48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>165</v>
+      <c r="H48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>166</v>
+        <v>229</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" s="1">
+        <v>231</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F49" s="1">
         <v>90.0</v>
       </c>
-      <c r="E49" s="1">
+      <c r="G49" s="1">
         <v>1910.0</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>168</v>
+      <c r="H49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>169</v>
+        <v>233</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>170</v>
+        <v>234</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D50" s="1">
+        <v>235</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F50" s="1">
         <v>80.0</v>
       </c>
-      <c r="E50" s="1">
+      <c r="G50" s="1">
         <v>1894.0</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>171</v>
+      <c r="H50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>173</v>
+        <v>238</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D51" s="1">
+        <v>238</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F51" s="1">
         <v>85.0</v>
       </c>
-      <c r="E51" s="1">
+      <c r="G51" s="1">
         <v>1895.0</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>174</v>
+      <c r="H51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>175</v>
+        <v>240</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>176</v>
+        <v>241</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D52" s="1">
+        <v>241</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F52" s="1">
         <v>95.0</v>
       </c>
-      <c r="E52" s="1">
+      <c r="G52" s="1">
         <v>1895.0</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>177</v>
+      <c r="H52" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>178</v>
+        <v>243</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>179</v>
+        <v>244</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D53" s="1">
+        <v>245</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" s="1">
         <v>85.0</v>
       </c>
-      <c r="E53" s="1">
+      <c r="G53" s="1">
         <v>1932.0</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>180</v>
+      <c r="H53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>182</v>
+        <v>248</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D54" s="1">
+        <v>249</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F54" s="1">
         <v>88.0</v>
       </c>
-      <c r="E54" s="1">
+      <c r="G54" s="1">
         <v>1911.0</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>183</v>
+      <c r="H54" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>184</v>
+        <v>251</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>185</v>
+        <v>252</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D55" s="1">
+        <v>253</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F55" s="1">
         <v>95.0</v>
       </c>
-      <c r="E55" s="1">
+      <c r="G55" s="1">
         <v>1908.0</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>186</v>
+      <c r="H55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>187</v>
+        <v>255</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D56" s="1">
+        <v>257</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F56" s="1">
         <v>80.0</v>
       </c>
-      <c r="E56" s="1">
+      <c r="G56" s="1">
         <v>1942.0</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>189</v>
+      <c r="H56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>190</v>
+        <v>259</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D57" s="1">
+        <v>261</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F57" s="1">
         <v>82.0</v>
       </c>
-      <c r="E57" s="1">
+      <c r="G57" s="1">
         <v>1910.0</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>192</v>
+      <c r="H57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>193</v>
+        <v>263</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>194</v>
+        <v>264</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D58" s="1">
+        <v>264</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58" s="1">
         <v>92.0</v>
       </c>
-      <c r="E58" s="1">
+      <c r="G58" s="1">
         <v>1909.0</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>195</v>
+      <c r="H58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>196</v>
+        <v>266</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D59" s="1">
+        <v>268</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F59" s="1">
         <v>85.0</v>
       </c>
-      <c r="E59" s="1">
+      <c r="G59" s="1">
         <v>1916.0</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>198</v>
+      <c r="H59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>199</v>
+        <v>270</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D60" s="1">
+        <v>272</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F60" s="1">
         <v>80.0</v>
       </c>
-      <c r="E60" s="1">
+      <c r="G60" s="1">
         <v>1936.0</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>201</v>
+      <c r="H60" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>202</v>
+        <v>274</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>203</v>
+        <v>275</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" s="1">
+        <v>276</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F61" s="1">
         <v>90.0</v>
       </c>
-      <c r="E61" s="1">
+      <c r="G61" s="1">
         <v>1934.0</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>204</v>
+      <c r="H61" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>205</v>
+        <v>278</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>206</v>
+        <v>279</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D62" s="1">
+        <v>280</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F62" s="1">
         <v>80.0</v>
       </c>
-      <c r="E62" s="1">
+      <c r="G62" s="1">
         <v>1890.0</v>
       </c>
-      <c r="F62" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>207</v>
+      <c r="H62" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>208</v>
+        <v>282</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>209</v>
+        <v>283</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D63" s="1">
+        <v>284</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F63" s="1">
         <v>88.0</v>
       </c>
-      <c r="E63" s="1">
+      <c r="G63" s="1">
         <v>1945.0</v>
       </c>
-      <c r="F63" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>210</v>
+      <c r="H63" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>211</v>
+        <v>286</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>212</v>
+        <v>287</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="1">
+        <v>288</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="1">
         <v>85.0</v>
       </c>
-      <c r="E64" s="1">
+      <c r="G64" s="1">
         <v>1928.0</v>
       </c>
-      <c r="F64" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>213</v>
+      <c r="H64" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>214</v>
+        <v>290</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D65" s="1">
+        <v>292</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F65" s="1">
         <v>85.0</v>
       </c>
-      <c r="E65" s="1">
+      <c r="G65" s="1">
         <v>1948.0</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>216</v>
+      <c r="H65" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>217</v>
+        <v>294</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>218</v>
+        <v>295</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D66" s="1">
+        <v>296</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F66" s="1">
         <v>95.0</v>
       </c>
-      <c r="E66" s="1">
+      <c r="G66" s="1">
         <v>1922.0</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>219</v>
+      <c r="H66" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>220</v>
+        <v>298</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>221</v>
+        <v>299</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D67" s="1">
+        <v>300</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F67" s="1">
         <v>88.0</v>
       </c>
-      <c r="E67" s="1">
+      <c r="G67" s="1">
         <v>1947.0</v>
       </c>
-      <c r="F67" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>222</v>
+      <c r="H67" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>224</v>
+        <v>303</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D68" s="1">
+        <v>304</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F68" s="1">
         <v>90.0</v>
       </c>
-      <c r="E68" s="1">
+      <c r="G68" s="1">
         <v>1916.0</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>225</v>
+      <c r="H68" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>226</v>
+        <v>306</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>227</v>
+        <v>307</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D69" s="1">
+        <v>308</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" s="1">
         <v>90.0</v>
       </c>
-      <c r="E69" s="1">
+      <c r="G69" s="1">
         <v>1906.0</v>
       </c>
-      <c r="F69" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>228</v>
+      <c r="H69" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>229</v>
+        <v>310</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>230</v>
+        <v>311</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D70" s="1">
+        <v>312</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70" s="1">
         <v>98.0</v>
       </c>
-      <c r="E70" s="1">
+      <c r="G70" s="1">
         <v>1906.0</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>231</v>
+      <c r="H70" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>232</v>
+        <v>314</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>233</v>
+        <v>315</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D71" s="1">
+        <v>316</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F71" s="1">
         <v>75.0</v>
       </c>
-      <c r="E71" s="1">
+      <c r="G71" s="1">
         <v>1935.0</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>234</v>
+      <c r="H71" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>235</v>
+        <v>318</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>236</v>
+        <v>319</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D72" s="1">
+        <v>320</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F72" s="1">
         <v>92.0</v>
       </c>
-      <c r="E72" s="1">
+      <c r="G72" s="1">
         <v>1924.0</v>
       </c>
-      <c r="F72" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>237</v>
+      <c r="H72" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>238</v>
+        <v>322</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D73" s="1">
+        <v>324</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F73" s="1">
         <v>85.0</v>
       </c>
-      <c r="E73" s="1">
+      <c r="G73" s="1">
         <v>1912.0</v>
       </c>
-      <c r="F73" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>240</v>
+      <c r="H73" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>241</v>
+        <v>326</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>242</v>
+        <v>327</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D74" s="1">
+        <v>328</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F74" s="1">
         <v>95.0</v>
       </c>
-      <c r="E74" s="1">
+      <c r="G74" s="1">
         <v>1916.0</v>
       </c>
-      <c r="F74" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>243</v>
+      <c r="H74" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>244</v>
+        <v>330</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>245</v>
+        <v>331</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D75" s="1">
+        <v>332</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F75" s="1">
         <v>92.0</v>
       </c>
-      <c r="E75" s="1">
+      <c r="G75" s="1">
         <v>1927.0</v>
       </c>
-      <c r="F75" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>246</v>
+      <c r="H75" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>247</v>
+        <v>334</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>248</v>
+        <v>335</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D76" s="1">
+        <v>336</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F76" s="1">
         <v>85.0</v>
       </c>
-      <c r="E76" s="1">
+      <c r="G76" s="1">
         <v>1943.0</v>
       </c>
-      <c r="F76" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>249</v>
+      <c r="H76" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>250</v>
+        <v>338</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>251</v>
+        <v>339</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D77" s="1">
+        <v>339</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F77" s="1">
         <v>90.0</v>
       </c>
-      <c r="E77" s="1">
+      <c r="G77" s="1">
         <v>1923.0</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>252</v>
+      <c r="H77" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>254</v>
+        <v>342</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D78" s="1">
+        <v>343</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F78" s="1">
         <v>88.0</v>
       </c>
-      <c r="E78" s="1">
+      <c r="G78" s="1">
         <v>1926.0</v>
       </c>
-      <c r="F78" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>255</v>
+      <c r="H78" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>256</v>
+        <v>345</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>257</v>
+        <v>346</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D79" s="1">
+        <v>347</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F79" s="1">
         <v>95.0</v>
       </c>
-      <c r="E79" s="1">
+      <c r="G79" s="1">
         <v>1918.0</v>
       </c>
-      <c r="F79" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>258</v>
+      <c r="H79" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>259</v>
+        <v>349</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D80" s="1">
+        <v>351</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F80" s="1">
         <v>98.0</v>
       </c>
-      <c r="E80" s="1">
+      <c r="G80" s="1">
         <v>1948.0</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>261</v>
+      <c r="H80" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>262</v>
+        <v>353</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>263</v>
+        <v>354</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D81" s="1">
+        <v>355</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F81" s="1">
         <v>90.0</v>
       </c>
-      <c r="E81" s="1">
+      <c r="G81" s="1">
         <v>1918.0</v>
       </c>
-      <c r="F81" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>264</v>
+      <c r="H81" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>265</v>
+        <v>357</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>266</v>
+        <v>358</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D82" s="1">
+        <v>359</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F82" s="1">
         <v>85.0</v>
       </c>
-      <c r="E82" s="1">
+      <c r="G82" s="1">
         <v>1929.0</v>
       </c>
-      <c r="F82" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>267</v>
+      <c r="H82" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>268</v>
+        <v>361</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>269</v>
+        <v>362</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D83" s="1">
+        <v>363</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F83" s="1">
         <v>80.0</v>
       </c>
-      <c r="E83" s="1">
+      <c r="G83" s="1">
         <v>1911.0</v>
       </c>
-      <c r="F83" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>270</v>
+      <c r="H83" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>272</v>
+        <v>366</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D84" s="1">
+        <v>367</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F84" s="1">
         <v>80.0</v>
       </c>
-      <c r="E84" s="1">
+      <c r="G84" s="1">
         <v>1911.0</v>
       </c>
-      <c r="F84" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>273</v>
+      <c r="H84" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>274</v>
+        <v>369</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>275</v>
+        <v>370</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D85" s="1">
+        <v>370</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F85" s="1">
         <v>98.0</v>
       </c>
-      <c r="E85" s="1">
+      <c r="G85" s="1">
         <v>1914.0</v>
       </c>
-      <c r="F85" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>276</v>
+      <c r="H85" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>277</v>
+        <v>372</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>278</v>
+        <v>373</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D86" s="1">
+        <v>374</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F86" s="1">
         <v>82.0</v>
       </c>
-      <c r="E86" s="1">
+      <c r="G86" s="1">
         <v>1929.0</v>
       </c>
-      <c r="F86" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>279</v>
+      <c r="H86" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>280</v>
+        <v>376</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>281</v>
+        <v>377</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D87" s="1">
+        <v>378</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F87" s="1">
         <v>80.0</v>
       </c>
-      <c r="E87" s="1">
+      <c r="G87" s="1">
         <v>1935.0</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>282</v>
+      <c r="H87" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>283</v>
+        <v>380</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>284</v>
+        <v>381</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D88" s="1">
+        <v>382</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F88" s="1">
         <v>90.0</v>
       </c>
-      <c r="E88" s="1">
+      <c r="G88" s="1">
         <v>1934.0</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>285</v>
+      <c r="H88" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>286</v>
+        <v>384</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>287</v>
+        <v>385</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D89" s="1">
+        <v>386</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F89" s="1">
         <v>92.0</v>
       </c>
-      <c r="E89" s="1">
+      <c r="G89" s="1">
         <v>1906.0</v>
       </c>
-      <c r="F89" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>288</v>
+      <c r="H89" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>289</v>
+        <v>388</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>290</v>
+        <v>389</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D90" s="1">
+        <v>390</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F90" s="1">
         <v>85.0</v>
       </c>
-      <c r="E90" s="1">
+      <c r="G90" s="1">
         <v>1917.0</v>
       </c>
-      <c r="F90" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>291</v>
+      <c r="H90" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>292</v>
+        <v>392</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>293</v>
+        <v>393</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D91" s="1">
+        <v>394</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F91" s="1">
         <v>90.0</v>
       </c>
-      <c r="E91" s="1">
+      <c r="G91" s="1">
         <v>1915.0</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>294</v>
+      <c r="H91" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>295</v>
+        <v>396</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>296</v>
+        <v>397</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D92" s="1">
+        <v>398</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F92" s="1">
         <v>88.0</v>
       </c>
-      <c r="E92" s="1">
+      <c r="G92" s="1">
         <v>1913.0</v>
       </c>
-      <c r="F92" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>297</v>
+      <c r="H92" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>298</v>
+        <v>400</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>299</v>
+        <v>401</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D93" s="1">
+        <v>402</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F93" s="1">
         <v>80.0</v>
       </c>
-      <c r="E93" s="1">
+      <c r="G93" s="1">
         <v>1909.0</v>
       </c>
-      <c r="F93" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>300</v>
+      <c r="H93" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>301</v>
+        <v>404</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>302</v>
+        <v>405</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D94" s="1">
+        <v>406</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F94" s="1">
         <v>85.0</v>
       </c>
-      <c r="E94" s="1">
+      <c r="G94" s="1">
         <v>1927.0</v>
       </c>
-      <c r="F94" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>303</v>
+      <c r="H94" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>304</v>
+        <v>408</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>305</v>
+        <v>409</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D95" s="1">
+        <v>410</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F95" s="1">
         <v>75.0</v>
       </c>
-      <c r="E95" s="1">
+      <c r="G95" s="1">
         <v>1910.0</v>
       </c>
-      <c r="F95" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>306</v>
+      <c r="H95" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>307</v>
+        <v>412</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>308</v>
+        <v>413</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D96" s="1">
+        <v>414</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F96" s="1">
         <v>95.0</v>
       </c>
-      <c r="E96" s="1">
+      <c r="G96" s="1">
         <v>1924.0</v>
       </c>
-      <c r="F96" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>309</v>
+      <c r="H96" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>310</v>
+        <v>416</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>311</v>
+        <v>417</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D97" s="1">
+        <v>418</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F97" s="1">
         <v>88.0</v>
       </c>
-      <c r="E97" s="1">
+      <c r="G97" s="1">
         <v>1921.0</v>
       </c>
-      <c r="F97" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>312</v>
+      <c r="H97" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>313</v>
+        <v>420</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>314</v>
+        <v>421</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D98" s="1">
+        <v>422</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F98" s="1">
         <v>80.0</v>
       </c>
-      <c r="E98" s="1">
+      <c r="G98" s="1">
         <v>1943.0</v>
       </c>
-      <c r="F98" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>315</v>
+      <c r="H98" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>316</v>
+        <v>424</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>317</v>
+        <v>425</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D99" s="1">
+        <v>426</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F99" s="1">
         <v>75.0</v>
       </c>
-      <c r="E99" s="1">
+      <c r="G99" s="1">
         <v>1936.0</v>
       </c>
-      <c r="F99" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>318</v>
+      <c r="H99" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>319</v>
+        <v>428</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>320</v>
+        <v>429</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D100" s="1">
+        <v>430</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F100" s="1">
         <v>85.0</v>
       </c>
-      <c r="E100" s="1">
+      <c r="G100" s="1">
         <v>1927.0</v>
       </c>
-      <c r="F100" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>321</v>
+      <c r="H100" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>322</v>
+        <v>432</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>323</v>
+        <v>433</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D101" s="1">
+        <v>434</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F101" s="1">
         <v>88.0</v>
       </c>
-      <c r="E101" s="1">
+      <c r="G101" s="1">
         <v>1912.0</v>
       </c>
-      <c r="F101" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>324</v>
+      <c r="H101" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>325</v>
+        <v>436</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>326</v>
+        <v>437</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D102" s="1">
+        <v>438</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F102" s="1">
         <v>80.0</v>
       </c>
-      <c r="E102" s="1">
+      <c r="G102" s="1">
         <v>1918.0</v>
       </c>
-      <c r="F102" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>327</v>
+      <c r="H102" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>328</v>
+        <v>440</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>329</v>
+        <v>441</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D103" s="1">
+        <v>442</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F103" s="1">
         <v>88.0</v>
       </c>
-      <c r="E103" s="1">
+      <c r="G103" s="1">
         <v>1948.0</v>
       </c>
-      <c r="F103" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>330</v>
+      <c r="H103" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>331</v>
+        <v>444</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>332</v>
+        <v>445</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D104" s="1">
+        <v>446</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F104" s="1">
         <v>85.0</v>
       </c>
-      <c r="E104" s="1">
+      <c r="G104" s="1">
         <v>1942.0</v>
       </c>
-      <c r="F104" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>333</v>
+      <c r="H104" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>334</v>
+        <v>448</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>335</v>
+        <v>449</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D105" s="1">
+        <v>450</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F105" s="1">
         <v>70.0</v>
       </c>
-      <c r="E105" s="1">
+      <c r="G105" s="1">
         <v>1947.0</v>
       </c>
-      <c r="F105" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>336</v>
+      <c r="H105" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>337</v>
+        <v>452</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>338</v>
+        <v>453</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D106" s="1">
+        <v>454</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="F106" s="1">
         <v>70.0</v>
       </c>
-      <c r="E106" s="1">
+      <c r="G106" s="1">
         <v>1907.0</v>
       </c>
-      <c r="F106" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>340</v>
+      <c r="H106" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>341</v>
+        <v>458</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>342</v>
+        <v>459</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D107" s="1">
+        <v>460</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F107" s="1">
         <v>90.0</v>
       </c>
-      <c r="E107" s="1">
+      <c r="G107" s="1">
         <v>1908.0</v>
       </c>
-      <c r="F107" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>343</v>
+      <c r="H107" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>344</v>
+        <v>462</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>345</v>
+        <v>463</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="D108" s="1">
+        <v>464</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="F108" s="1">
         <v>80.0</v>
       </c>
-      <c r="E108" s="1">
+      <c r="G108" s="1">
         <v>1888.0</v>
       </c>
-      <c r="F108" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>347</v>
+      <c r="H108" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>348</v>
+        <v>468</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>349</v>
+        <v>469</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D109" s="1">
+        <v>470</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F109" s="1">
         <v>80.0</v>
       </c>
-      <c r="E109" s="1">
+      <c r="G109" s="1">
         <v>1895.0</v>
       </c>
-      <c r="F109" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>350</v>
+      <c r="H109" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>351</v>
+        <v>472</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>352</v>
+        <v>473</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="D110" s="1">
+        <v>474</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="F110" s="1">
         <v>85.0</v>
       </c>
-      <c r="E110" s="1">
+      <c r="G110" s="1">
         <v>1906.0</v>
       </c>
-      <c r="F110" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>354</v>
+      <c r="H110" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
-        <v>355</v>
+        <v>478</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>356</v>
+        <v>479</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="D111" s="1">
+        <v>480</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F111" s="1">
         <v>95.0</v>
       </c>
-      <c r="E111" s="1">
+      <c r="G111" s="1">
         <v>1932.0</v>
       </c>
-      <c r="F111" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>358</v>
+      <c r="H111" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
-        <v>359</v>
+        <v>484</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>360</v>
+        <v>485</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D112" s="1">
+        <v>486</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F112" s="1">
         <v>90.0</v>
       </c>
-      <c r="E112" s="1">
+      <c r="G112" s="1">
         <v>1946.0</v>
       </c>
-      <c r="F112" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>361</v>
+      <c r="H112" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
-        <v>362</v>
+        <v>488</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>363</v>
+        <v>489</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="D113" s="1">
+        <v>490</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F113" s="1">
         <v>92.0</v>
       </c>
-      <c r="E113" s="1">
+      <c r="G113" s="1">
         <v>1943.0</v>
       </c>
-      <c r="F113" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>364</v>
+      <c r="H113" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>365</v>
+        <v>492</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>366</v>
+        <v>493</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D114" s="1">
+        <v>494</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F114" s="1">
         <v>80.0</v>
       </c>
-      <c r="E114" s="1">
+      <c r="G114" s="1">
         <v>1915.0</v>
       </c>
-      <c r="F114" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>367</v>
+      <c r="H114" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>368</v>
+        <v>496</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>369</v>
+        <v>497</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D115" s="1">
+        <v>498</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F115" s="1">
         <v>88.0</v>
       </c>
-      <c r="E115" s="1">
+      <c r="G115" s="1">
         <v>1939.0</v>
       </c>
-      <c r="F115" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>370</v>
+      <c r="H115" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>371</v>
+        <v>500</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>372</v>
+        <v>501</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="D116" s="1">
+        <v>502</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F116" s="1">
         <v>85.0</v>
       </c>
-      <c r="E116" s="1">
+      <c r="G116" s="1">
         <v>1934.0</v>
       </c>
-      <c r="F116" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>374</v>
+      <c r="H116" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>375</v>
+        <v>506</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>376</v>
+        <v>507</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="D117" s="1">
+        <v>508</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F117" s="1">
         <v>82.0</v>
       </c>
-      <c r="E117" s="1">
+      <c r="G117" s="1">
         <v>1938.0</v>
       </c>
-      <c r="F117" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>377</v>
+      <c r="H117" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>378</v>
+        <v>510</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>379</v>
+        <v>511</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D118" s="1">
+        <v>512</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="F118" s="1">
         <v>75.0</v>
       </c>
-      <c r="E118" s="1">
+      <c r="G118" s="1">
         <v>1937.0</v>
       </c>
-      <c r="F118" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>381</v>
+      <c r="H118" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>382</v>
+        <v>516</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>383</v>
+        <v>517</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D119" s="1">
+        <v>518</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="F119" s="1">
         <v>70.0</v>
       </c>
-      <c r="E119" s="1">
+      <c r="G119" s="1">
         <v>1937.0</v>
       </c>
-      <c r="F119" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>384</v>
+      <c r="H119" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>385</v>
+        <v>520</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>386</v>
+        <v>521</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D120" s="1">
+        <v>522</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F120" s="1">
         <v>75.0</v>
       </c>
-      <c r="E120" s="1">
+      <c r="G120" s="1">
         <v>1895.0</v>
       </c>
-      <c r="F120" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>387</v>
+      <c r="H120" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
-        <v>388</v>
+        <v>524</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>389</v>
+        <v>525</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="D121" s="1">
+        <v>526</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="F121" s="1">
         <v>85.0</v>
       </c>
-      <c r="E121" s="1">
+      <c r="G121" s="1">
         <v>1918.0</v>
       </c>
-      <c r="F121" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>391</v>
+      <c r="H121" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>392</v>
+        <v>530</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>393</v>
+        <v>531</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="D122" s="1">
+        <v>532</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="F122" s="1">
         <v>75.0</v>
       </c>
-      <c r="E122" s="1">
+      <c r="G122" s="1">
         <v>1946.0</v>
       </c>
-      <c r="F122" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>395</v>
+      <c r="H122" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>396</v>
+        <v>536</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>397</v>
+        <v>537</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D123" s="1">
+        <v>538</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F123" s="1">
         <v>88.0</v>
       </c>
-      <c r="E123" s="1">
+      <c r="G123" s="1">
         <v>1922.0</v>
       </c>
-      <c r="F123" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>398</v>
+      <c r="H123" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>399</v>
+        <v>540</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>400</v>
+        <v>541</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="D124" s="1">
+        <v>542</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="F124" s="1">
         <v>98.0</v>
       </c>
-      <c r="E124" s="1">
+      <c r="G124" s="1">
         <v>1872.0</v>
       </c>
-      <c r="F124" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>402</v>
+      <c r="H124" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>403</v>
+        <v>546</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>404</v>
+        <v>547</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="D125" s="1">
+        <v>548</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="F125" s="1">
         <v>90.0</v>
       </c>
-      <c r="E125" s="1">
+      <c r="G125" s="1">
         <v>1940.0</v>
       </c>
-      <c r="F125" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>405</v>
+      <c r="H125" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>406</v>
+        <v>550</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>407</v>
+        <v>551</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="D126" s="1">
+        <v>552</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="F126" s="1">
         <v>85.0</v>
       </c>
-      <c r="E126" s="1">
+      <c r="G126" s="1">
         <v>1920.0</v>
       </c>
-      <c r="F126" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>408</v>
+      <c r="H126" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>409</v>
+        <v>554</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>410</v>
+        <v>555</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D127" s="1">
+        <v>556</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F127" s="1">
         <v>92.0</v>
       </c>
-      <c r="E127" s="1">
+      <c r="G127" s="1">
         <v>1920.0</v>
       </c>
-      <c r="F127" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>411</v>
+      <c r="H127" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>412</v>
+        <v>558</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>413</v>
+        <v>559</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="D128" s="1">
+        <v>560</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="F128" s="1">
         <v>75.0</v>
       </c>
-      <c r="E128" s="1">
+      <c r="G128" s="1">
         <v>1940.0</v>
       </c>
-      <c r="F128" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>415</v>
+      <c r="H128" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
-        <v>416</v>
+        <v>564</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>417</v>
+        <v>565</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="D129" s="1">
+        <v>566</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F129" s="1">
         <v>88.0</v>
       </c>
-      <c r="E129" s="1">
+      <c r="G129" s="1">
         <v>1898.0</v>
       </c>
-      <c r="F129" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>419</v>
+      <c r="H129" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>420</v>
+        <v>570</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>421</v>
+        <v>571</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="D130" s="1">
+        <v>572</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="F130" s="1">
         <v>85.0</v>
       </c>
-      <c r="E130" s="1">
+      <c r="G130" s="1">
         <v>1919.0</v>
       </c>
-      <c r="F130" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>423</v>
+      <c r="H130" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>424</v>
+        <v>576</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>425</v>
+        <v>577</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="D131" s="1">
+        <v>578</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="F131" s="1">
         <v>90.0</v>
       </c>
-      <c r="E131" s="1">
+      <c r="G131" s="1">
         <v>1901.0</v>
       </c>
-      <c r="F131" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>427</v>
+      <c r="H131" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
-        <v>428</v>
+        <v>582</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>429</v>
+        <v>583</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="D132" s="1">
+        <v>584</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="F132" s="1">
         <v>70.0</v>
       </c>
-      <c r="E132" s="1">
+      <c r="G132" s="1">
         <v>1896.0</v>
       </c>
-      <c r="F132" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>431</v>
+      <c r="H132" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>432</v>
+        <v>588</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>433</v>
+        <v>589</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D133" s="1">
+        <v>590</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="F133" s="1">
         <v>88.0</v>
       </c>
-      <c r="E133" s="1">
+      <c r="G133" s="1">
         <v>1907.0</v>
       </c>
-      <c r="F133" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>434</v>
+      <c r="H133" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>435</v>
+        <v>592</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>436</v>
+        <v>593</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="D134" s="1">
+        <v>594</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="F134" s="1">
         <v>85.0</v>
       </c>
-      <c r="E134" s="1">
+      <c r="G134" s="1">
         <v>1887.0</v>
       </c>
-      <c r="F134" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>438</v>
+      <c r="H134" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
-        <v>439</v>
+        <v>598</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>440</v>
+        <v>599</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D135" s="1">
+        <v>600</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F135" s="1">
         <v>80.0</v>
       </c>
-      <c r="E135" s="1">
+      <c r="G135" s="1">
         <v>1947.0</v>
       </c>
-      <c r="F135" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>441</v>
+      <c r="H135" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
-        <v>442</v>
+        <v>602</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>443</v>
+        <v>603</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="D136" s="1">
+        <v>604</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="F136" s="1">
         <v>75.0</v>
       </c>
-      <c r="E136" s="1">
+      <c r="G136" s="1">
         <v>1934.0</v>
       </c>
-      <c r="F136" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>445</v>
+      <c r="H136" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>446</v>
+        <v>608</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>447</v>
+        <v>609</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D137" s="1">
+        <v>610</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="F137" s="1">
         <v>88.0</v>
       </c>
-      <c r="E137" s="1">
+      <c r="G137" s="1">
         <v>1897.0</v>
       </c>
-      <c r="F137" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>449</v>
+      <c r="H137" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>
